--- a/openpyxl/test.xlsx
+++ b/openpyxl/test.xlsx
@@ -413,9 +413,92 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A1"/>
+  <dimension ref="A1:F8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>hello</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>bye</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>python</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>python</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>python</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>python</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>python</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>python</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>python</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>python</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>python</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>python</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>python</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>python</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>